--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229445</v>
+        <v>120229510</v>
       </c>
       <c r="B2" t="n">
-        <v>5189</v>
+        <v>91272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -724,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655214</v>
+        <v>655235</v>
       </c>
       <c r="R2" t="n">
-        <v>6681515</v>
+        <v>6681455</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -759,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229510</v>
+        <v>120229626</v>
       </c>
       <c r="B3" t="n">
-        <v>91254</v>
+        <v>103441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,26 +806,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655235</v>
+        <v>655258</v>
       </c>
       <c r="R3" t="n">
-        <v>6681455</v>
+        <v>6681471</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229494</v>
+        <v>120229499</v>
       </c>
       <c r="B4" t="n">
-        <v>91182</v>
+        <v>91200</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -954,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655013</v>
+        <v>655191</v>
       </c>
       <c r="R4" t="n">
-        <v>6681312</v>
+        <v>6681506</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229626</v>
+        <v>120229494</v>
       </c>
       <c r="B5" t="n">
-        <v>103418</v>
+        <v>91200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,27 +1037,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1070,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655258</v>
+        <v>655013</v>
       </c>
       <c r="R5" t="n">
-        <v>6681471</v>
+        <v>6681312</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1105,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229499</v>
+        <v>120229445</v>
       </c>
       <c r="B6" t="n">
-        <v>91182</v>
+        <v>5189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,26 +1152,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655191</v>
+        <v>655214</v>
       </c>
       <c r="R6" t="n">
-        <v>6681506</v>
+        <v>6681515</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229510</v>
+        <v>120229499</v>
       </c>
       <c r="B2" t="n">
-        <v>91272</v>
+        <v>91200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655235</v>
+        <v>655191</v>
       </c>
       <c r="R2" t="n">
-        <v>6681455</v>
+        <v>6681506</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229626</v>
+        <v>120229510</v>
       </c>
       <c r="B3" t="n">
-        <v>103441</v>
+        <v>91272</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,27 +806,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -834,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655258</v>
+        <v>655235</v>
       </c>
       <c r="R3" t="n">
-        <v>6681471</v>
+        <v>6681455</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -869,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -879,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,7 +905,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229499</v>
+        <v>120229494</v>
       </c>
       <c r="B4" t="n">
         <v>91200</v>
@@ -949,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655191</v>
+        <v>655013</v>
       </c>
       <c r="R4" t="n">
-        <v>6681506</v>
+        <v>6681312</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -984,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229494</v>
+        <v>120229626</v>
       </c>
       <c r="B5" t="n">
-        <v>91200</v>
+        <v>103441</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,26 +1036,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655013</v>
+        <v>655258</v>
       </c>
       <c r="R5" t="n">
-        <v>6681312</v>
+        <v>6681471</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229499</v>
+        <v>120229510</v>
       </c>
       <c r="B2" t="n">
-        <v>91200</v>
+        <v>91272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655191</v>
+        <v>655235</v>
       </c>
       <c r="R2" t="n">
-        <v>6681506</v>
+        <v>6681455</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229510</v>
+        <v>120229494</v>
       </c>
       <c r="B3" t="n">
-        <v>91272</v>
+        <v>91200</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655235</v>
+        <v>655013</v>
       </c>
       <c r="R3" t="n">
-        <v>6681455</v>
+        <v>6681312</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +868,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229494</v>
+        <v>120229445</v>
       </c>
       <c r="B4" t="n">
-        <v>91200</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,26 +921,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655013</v>
+        <v>655214</v>
       </c>
       <c r="R4" t="n">
-        <v>6681312</v>
+        <v>6681515</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -983,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229626</v>
+        <v>120229499</v>
       </c>
       <c r="B5" t="n">
-        <v>103441</v>
+        <v>91200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,27 +1042,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>1339</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1064,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655258</v>
+        <v>655191</v>
       </c>
       <c r="R5" t="n">
-        <v>6681471</v>
+        <v>6681506</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1099,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229445</v>
+        <v>120229626</v>
       </c>
       <c r="B6" t="n">
-        <v>5189</v>
+        <v>103441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,32 +1157,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655214</v>
+        <v>655258</v>
       </c>
       <c r="R6" t="n">
-        <v>6681515</v>
+        <v>6681471</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -905,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229445</v>
+        <v>120229626</v>
       </c>
       <c r="B4" t="n">
-        <v>5189</v>
+        <v>103441</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,32 +921,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655214</v>
+        <v>655258</v>
       </c>
       <c r="R4" t="n">
-        <v>6681515</v>
+        <v>6681471</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1141,10 +1136,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229626</v>
+        <v>120229445</v>
       </c>
       <c r="B6" t="n">
-        <v>103441</v>
+        <v>5189</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,27 +1152,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655258</v>
+        <v>655214</v>
       </c>
       <c r="R6" t="n">
-        <v>6681471</v>
+        <v>6681515</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229510</v>
+        <v>120229499</v>
       </c>
       <c r="B2" t="n">
-        <v>91272</v>
+        <v>91200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655235</v>
+        <v>655191</v>
       </c>
       <c r="R2" t="n">
-        <v>6681455</v>
+        <v>6681506</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229494</v>
+        <v>120229445</v>
       </c>
       <c r="B3" t="n">
-        <v>91200</v>
+        <v>5189</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,26 +806,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1339</v>
+        <v>105930</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655013</v>
+        <v>655214</v>
       </c>
       <c r="R3" t="n">
-        <v>6681312</v>
+        <v>6681515</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -868,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -878,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229626</v>
+        <v>120229510</v>
       </c>
       <c r="B4" t="n">
-        <v>103441</v>
+        <v>91272</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,27 +927,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -949,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655258</v>
+        <v>655235</v>
       </c>
       <c r="R4" t="n">
-        <v>6681471</v>
+        <v>6681455</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -984,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229499</v>
+        <v>120229494</v>
       </c>
       <c r="B5" t="n">
         <v>91200</v>
@@ -1064,10 +1069,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655191</v>
+        <v>655013</v>
       </c>
       <c r="R5" t="n">
-        <v>6681506</v>
+        <v>6681312</v>
       </c>
       <c r="S5" t="n">
         <v>4</v>
@@ -1099,7 +1104,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1114,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229445</v>
+        <v>120229626</v>
       </c>
       <c r="B6" t="n">
-        <v>5189</v>
+        <v>103441</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,32 +1157,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655214</v>
+        <v>655258</v>
       </c>
       <c r="R6" t="n">
-        <v>6681515</v>
+        <v>6681471</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,6 +1254,1681 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120499836</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>655037</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6681471</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120495656</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90564</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4660</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rävticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Inocutis rheades</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>655401</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6681567</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120496798</v>
+      </c>
+      <c r="B9" t="n">
+        <v>94550</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>210</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>655231</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6681523</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120497099</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>655229</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6681516</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120498279</v>
+      </c>
+      <c r="B11" t="n">
+        <v>5169</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>655176</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6681491</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120497668</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57326</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>655206</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6681496</v>
+      </c>
+      <c r="S12" t="n">
+        <v>30</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120496936</v>
+      </c>
+      <c r="B13" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>655210</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6681498</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120497044</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>655213</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6681503</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120500418</v>
+      </c>
+      <c r="B15" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>655161</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6681641</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120498507</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>655132</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6681443</v>
+      </c>
+      <c r="S16" t="n">
+        <v>50</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120497208</v>
+      </c>
+      <c r="B17" t="n">
+        <v>94550</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>210</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>655213</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6681513</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120497440</v>
+      </c>
+      <c r="B18" t="n">
+        <v>94550</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>210</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Buxbaumia viridis</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>655206</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6681520</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120499877</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91272</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>655044</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6681469</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2930,6 +2930,1173 @@
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120498166</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>655161</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6681506</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Med gigantisk klibbticka.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120498244</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>655170</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6681498</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120499974</v>
+      </c>
+      <c r="B22" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>655059</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6681472</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bara gran och björk i närheten.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120500284</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>655136</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6681501</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120499637</v>
+      </c>
+      <c r="B24" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>654995</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6681443</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:02</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>120499168</v>
+      </c>
+      <c r="B25" t="n">
+        <v>90781</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>654913</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6681354</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>120525350</v>
+      </c>
+      <c r="B26" t="n">
+        <v>94454</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>655231</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6681523</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>På samma låga som grön sköldmossa.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>120525413</v>
+      </c>
+      <c r="B27" t="n">
+        <v>94454</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>655206</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6681520</v>
+      </c>
+      <c r="S27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På samma låga som grön sköldmossa.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>120498000</v>
+      </c>
+      <c r="B28" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>655170</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6681510</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229499</v>
+        <v>120229510</v>
       </c>
       <c r="B2" t="n">
-        <v>91200</v>
+        <v>91272</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1339</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655191</v>
+        <v>655235</v>
       </c>
       <c r="R2" t="n">
-        <v>6681506</v>
+        <v>6681455</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229445</v>
+        <v>120229626</v>
       </c>
       <c r="B3" t="n">
-        <v>5189</v>
+        <v>103441</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,32 +806,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655214</v>
+        <v>655258</v>
       </c>
       <c r="R3" t="n">
-        <v>6681515</v>
+        <v>6681471</v>
       </c>
       <c r="S3" t="n">
         <v>4</v>
@@ -874,7 +869,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +879,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -911,10 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229510</v>
+        <v>120229445</v>
       </c>
       <c r="B4" t="n">
-        <v>91272</v>
+        <v>5189</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,26 +922,32 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>105930</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -954,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655235</v>
+        <v>655214</v>
       </c>
       <c r="R4" t="n">
-        <v>6681455</v>
+        <v>6681515</v>
       </c>
       <c r="S4" t="n">
         <v>4</v>
@@ -989,7 +990,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1000,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1141,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229626</v>
+        <v>120229499</v>
       </c>
       <c r="B6" t="n">
-        <v>103441</v>
+        <v>91200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1157,27 +1158,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222412</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655258</v>
+        <v>655191</v>
       </c>
       <c r="R6" t="n">
-        <v>6681471</v>
+        <v>6681506</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120499836</v>
+        <v>120497668</v>
       </c>
       <c r="B7" t="n">
-        <v>5189</v>
+        <v>57326</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,20 +1269,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105930</v>
+        <v>100048</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1290,10 +1290,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1302,13 +1306,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655037</v>
+        <v>655206</v>
       </c>
       <c r="R7" t="n">
-        <v>6681471</v>
+        <v>6681496</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1337,7 +1341,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1347,7 +1351,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,21 +1362,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1389,10 +1378,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120495656</v>
+        <v>120498279</v>
       </c>
       <c r="B8" t="n">
-        <v>90564</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1405,34 +1394,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4660</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655401</v>
+        <v>655176</v>
       </c>
       <c r="R8" t="n">
-        <v>6681567</v>
+        <v>6681491</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1464,7 +1458,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1474,7 +1468,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,17 +1482,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1516,10 +1510,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120496798</v>
+        <v>120499836</v>
       </c>
       <c r="B9" t="n">
-        <v>94550</v>
+        <v>5189</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1532,31 +1526,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1565,10 +1555,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655231</v>
+        <v>655037</v>
       </c>
       <c r="R9" t="n">
-        <v>6681523</v>
+        <v>6681471</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1600,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1610,7 +1600,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1652,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120497099</v>
+        <v>120496798</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>94550</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1664,35 +1654,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1701,13 +1691,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655229</v>
+        <v>655231</v>
       </c>
       <c r="R10" t="n">
-        <v>6681516</v>
+        <v>6681523</v>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1736,7 +1726,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1746,7 +1736,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1757,6 +1747,21 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1773,10 +1778,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120498279</v>
+        <v>120495656</v>
       </c>
       <c r="B11" t="n">
-        <v>5169</v>
+        <v>90564</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,39 +1794,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>4660</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655176</v>
+        <v>655401</v>
       </c>
       <c r="R11" t="n">
-        <v>6681491</v>
+        <v>6681567</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1877,17 +1877,17 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120497668</v>
+        <v>120500418</v>
       </c>
       <c r="B12" t="n">
-        <v>57326</v>
+        <v>91200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1917,50 +1917,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100048</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655206</v>
+        <v>655161</v>
       </c>
       <c r="R12" t="n">
-        <v>6681496</v>
+        <v>6681641</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1989,7 +1980,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1999,7 +1990,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2010,6 +2001,21 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2026,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120496936</v>
+        <v>120497044</v>
       </c>
       <c r="B13" t="n">
-        <v>5189</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2038,43 +2044,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655210</v>
+        <v>655213</v>
       </c>
       <c r="R13" t="n">
-        <v>6681498</v>
+        <v>6681503</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2106,7 +2107,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2116,7 +2117,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,10 +2159,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120497044</v>
+        <v>120497099</v>
       </c>
       <c r="B14" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2174,37 +2175,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655213</v>
+        <v>655229</v>
       </c>
       <c r="R14" t="n">
-        <v>6681503</v>
+        <v>6681516</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2233,7 +2243,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2243,7 +2253,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2254,21 +2264,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2285,10 +2280,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120500418</v>
+        <v>120498507</v>
       </c>
       <c r="B15" t="n">
-        <v>91200</v>
+        <v>57473</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2297,41 +2292,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655161</v>
+        <v>655132</v>
       </c>
       <c r="R15" t="n">
-        <v>6681641</v>
+        <v>6681443</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2360,7 +2364,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2370,7 +2374,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2381,21 +2385,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2412,10 +2401,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120498507</v>
+        <v>120499877</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>91272</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2424,50 +2413,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655132</v>
+        <v>655044</v>
       </c>
       <c r="R16" t="n">
-        <v>6681443</v>
+        <v>6681469</v>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2496,7 +2476,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2506,7 +2486,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2517,6 +2497,21 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2533,10 +2528,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120497208</v>
+        <v>120496936</v>
       </c>
       <c r="B17" t="n">
-        <v>94550</v>
+        <v>5189</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2549,31 +2544,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2582,10 +2573,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655213</v>
+        <v>655210</v>
       </c>
       <c r="R17" t="n">
-        <v>6681513</v>
+        <v>6681498</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2617,7 +2608,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2627,7 +2618,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2669,10 +2660,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120497440</v>
+        <v>120500284</v>
       </c>
       <c r="B18" t="n">
-        <v>94550</v>
+        <v>91200</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2685,43 +2676,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655206</v>
+        <v>655136</v>
       </c>
       <c r="R18" t="n">
-        <v>6681520</v>
+        <v>6681501</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2753,7 +2735,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2763,7 +2745,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2805,10 +2787,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120499877</v>
+        <v>120498166</v>
       </c>
       <c r="B19" t="n">
-        <v>91272</v>
+        <v>91200</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2821,21 +2803,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2845,10 +2827,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655044</v>
+        <v>655161</v>
       </c>
       <c r="R19" t="n">
-        <v>6681469</v>
+        <v>6681506</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2880,7 +2862,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2890,7 +2872,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Med gigantisk klibbticka.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2932,10 +2919,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120498166</v>
+        <v>120499168</v>
       </c>
       <c r="B20" t="n">
-        <v>91200</v>
+        <v>90781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2944,38 +2931,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>655161</v>
+        <v>654913</v>
       </c>
       <c r="R20" t="n">
-        <v>6681506</v>
+        <v>6681354</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3007,7 +2994,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3017,12 +3004,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Med gigantisk klibbticka.</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3191,10 +3173,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120499974</v>
+        <v>120498000</v>
       </c>
       <c r="B22" t="n">
-        <v>91879</v>
+        <v>91200</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3207,43 +3189,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5964</v>
+        <v>1339</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655059</v>
+        <v>655170</v>
       </c>
       <c r="R22" t="n">
-        <v>6681472</v>
+        <v>6681510</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3275,7 +3248,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3285,12 +3258,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bara gran och björk i närheten.</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3301,6 +3269,21 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3317,7 +3300,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120500284</v>
+        <v>120499637</v>
       </c>
       <c r="B23" t="n">
         <v>91200</v>
@@ -3357,10 +3340,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655136</v>
+        <v>654995</v>
       </c>
       <c r="R23" t="n">
-        <v>6681501</v>
+        <v>6681443</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3392,7 +3375,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3402,7 +3385,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3444,10 +3427,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120499637</v>
+        <v>120525350</v>
       </c>
       <c r="B24" t="n">
-        <v>91200</v>
+        <v>94454</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3460,37 +3443,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654995</v>
+        <v>655231</v>
       </c>
       <c r="R24" t="n">
-        <v>6681443</v>
+        <v>6681523</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3519,7 +3506,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3529,7 +3516,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>På samma låga som grön sköldmossa.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3538,6 +3530,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3571,10 +3564,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120499168</v>
+        <v>120535635</v>
       </c>
       <c r="B25" t="n">
-        <v>90781</v>
+        <v>80499</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3583,41 +3576,44 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1106</v>
+        <v>1049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654913</v>
+        <v>654985</v>
       </c>
       <c r="R25" t="n">
-        <v>6681354</v>
+        <v>6681219</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3641,22 +3637,27 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Riklig förekomst på gammal torr stubbe med gul, hård ved.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3665,23 +3666,9 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3698,10 +3685,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120525350</v>
+        <v>120534782</v>
       </c>
       <c r="B26" t="n">
-        <v>94454</v>
+        <v>80499</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3710,42 +3697,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2818</v>
+        <v>1049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655231</v>
+        <v>654967</v>
       </c>
       <c r="R26" t="n">
-        <v>6681523</v>
+        <v>6681292</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3772,27 +3755,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På samma låga som grön sköldmossa.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3801,24 +3779,8 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3835,14 +3797,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120525413</v>
+        <v>120497208</v>
       </c>
       <c r="B27" t="n">
-        <v>94454</v>
+        <v>94550</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3851,41 +3813,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655206</v>
+        <v>655213</v>
       </c>
       <c r="R27" t="n">
-        <v>6681520</v>
+        <v>6681513</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3914,7 +3881,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3924,12 +3891,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På samma låga som grön sköldmossa.</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3938,7 +3900,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3972,14 +3933,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120498000</v>
+        <v>120497440</v>
       </c>
       <c r="B28" t="n">
-        <v>91200</v>
+        <v>94550</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3988,34 +3949,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1339</v>
+        <v>210</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655170</v>
+        <v>655206</v>
       </c>
       <c r="R28" t="n">
-        <v>6681510</v>
+        <v>6681520</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4047,7 +4017,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -4057,7 +4027,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4096,6 +4066,2236 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>120533398</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>655229</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6681479</v>
+      </c>
+      <c r="S29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>120534340</v>
+      </c>
+      <c r="B30" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>655029</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6681228</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Enstaka plantor.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>120537714</v>
+      </c>
+      <c r="B31" t="n">
+        <v>94454</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>655100</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6681222</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På klen, riktigt murken granlåga i fuktig miljö.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>120538144</v>
+      </c>
+      <c r="B32" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>655174</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6681223</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>I bättre begagnat skick. Bara gran runtom.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>120535048</v>
+      </c>
+      <c r="B33" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>654966</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6681257</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>120499974</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91879</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus s.str.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>655059</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6681472</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bara gran och björk i närheten.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>120537910</v>
+      </c>
+      <c r="B35" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>655176</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6681218</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:50</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>120534972</v>
+      </c>
+      <c r="B36" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>654933</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6681283</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>120537301</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>655025</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6681224</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>120525413</v>
+      </c>
+      <c r="B38" t="n">
+        <v>94454</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>655206</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6681520</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-10-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På samma låga som grön sköldmossa.</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>120533674</v>
+      </c>
+      <c r="B39" t="n">
+        <v>103441</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>655158</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6681101</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Några småplantor.</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>120534339</v>
+      </c>
+      <c r="B40" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>655046</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6681223</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>120533660</v>
+      </c>
+      <c r="B41" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>655173</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6681110</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>120534702</v>
+      </c>
+      <c r="B42" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>654972</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6681278</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>120533496</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100194</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>655277</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6681282</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Bara enstaka plantor.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>120533945</v>
+      </c>
+      <c r="B44" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>655142</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6681116</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>120534505</v>
+      </c>
+      <c r="B45" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>655054</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6681371</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>120536842</v>
+      </c>
+      <c r="B46" t="n">
+        <v>5189</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>654967</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6681250</v>
+      </c>
+      <c r="S46" t="n">
+        <v>5</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229510</v>
+        <v>120229499</v>
       </c>
       <c r="B2" t="n">
-        <v>91272</v>
+        <v>91200</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655235</v>
+        <v>655191</v>
       </c>
       <c r="R2" t="n">
-        <v>6681455</v>
+        <v>6681506</v>
       </c>
       <c r="S2" t="n">
         <v>4</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229499</v>
+        <v>120229510</v>
       </c>
       <c r="B6" t="n">
-        <v>91200</v>
+        <v>91272</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1158,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>3298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655191</v>
+        <v>655235</v>
       </c>
       <c r="R6" t="n">
-        <v>6681506</v>
+        <v>6681455</v>
       </c>
       <c r="S6" t="n">
         <v>4</v>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120497668</v>
+        <v>120499836</v>
       </c>
       <c r="B7" t="n">
-        <v>57326</v>
+        <v>5189</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,20 +1269,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100048</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1290,14 +1290,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1306,13 +1302,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655206</v>
+        <v>655037</v>
       </c>
       <c r="R7" t="n">
-        <v>6681496</v>
+        <v>6681471</v>
       </c>
       <c r="S7" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1341,7 +1337,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1351,7 +1347,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,6 +1358,21 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1378,10 +1389,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120498279</v>
+        <v>120495656</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>90564</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,39 +1405,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655176</v>
+        <v>655401</v>
       </c>
       <c r="R8" t="n">
-        <v>6681491</v>
+        <v>6681567</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1458,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1468,7 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,17 +1488,17 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1510,10 +1516,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120499836</v>
+        <v>120497668</v>
       </c>
       <c r="B9" t="n">
-        <v>5189</v>
+        <v>57326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1522,20 +1528,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>105930</v>
+        <v>100048</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1543,10 +1549,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1555,13 +1565,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655037</v>
+        <v>655206</v>
       </c>
       <c r="R9" t="n">
-        <v>6681471</v>
+        <v>6681496</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1590,7 +1600,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,7 +1610,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,21 +1621,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1642,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120496798</v>
+        <v>120498279</v>
       </c>
       <c r="B10" t="n">
-        <v>94550</v>
+        <v>5169</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,31 +1653,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>210</v>
+        <v>100526</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1691,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655231</v>
+        <v>655176</v>
       </c>
       <c r="R10" t="n">
-        <v>6681523</v>
+        <v>6681491</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1726,7 +1717,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1736,7 +1727,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1778,10 +1769,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120495656</v>
+        <v>120498507</v>
       </c>
       <c r="B11" t="n">
-        <v>90564</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1790,41 +1781,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4660</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655401</v>
+        <v>655132</v>
       </c>
       <c r="R11" t="n">
-        <v>6681567</v>
+        <v>6681443</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1863,7 +1863,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,21 +1874,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1905,10 +1890,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120500418</v>
+        <v>120496936</v>
       </c>
       <c r="B12" t="n">
-        <v>91200</v>
+        <v>5189</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1921,34 +1906,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1339</v>
+        <v>105930</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655161</v>
+        <v>655210</v>
       </c>
       <c r="R12" t="n">
-        <v>6681641</v>
+        <v>6681498</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1980,7 +1970,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1990,7 +1980,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,10 +2022,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120497044</v>
+        <v>120499877</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>91272</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,25 +2034,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2072,10 +2062,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655213</v>
+        <v>655044</v>
       </c>
       <c r="R13" t="n">
-        <v>6681503</v>
+        <v>6681469</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,7 +2097,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2117,7 +2107,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2159,10 +2149,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120497099</v>
+        <v>120496798</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>94550</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2171,35 +2161,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2208,13 +2198,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655229</v>
+        <v>655231</v>
       </c>
       <c r="R14" t="n">
-        <v>6681516</v>
+        <v>6681523</v>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2243,7 +2233,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2253,7 +2243,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,6 +2254,21 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2280,10 +2285,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120498507</v>
+        <v>120500418</v>
       </c>
       <c r="B15" t="n">
-        <v>57473</v>
+        <v>91200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2292,50 +2297,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655132</v>
+        <v>655161</v>
       </c>
       <c r="R15" t="n">
-        <v>6681443</v>
+        <v>6681641</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2364,7 +2360,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2374,7 +2370,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2385,6 +2381,21 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2401,10 +2412,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120499877</v>
+        <v>120497099</v>
       </c>
       <c r="B16" t="n">
-        <v>91272</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2413,41 +2424,50 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655044</v>
+        <v>655229</v>
       </c>
       <c r="R16" t="n">
-        <v>6681469</v>
+        <v>6681516</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2476,7 +2496,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2486,7 +2506,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2497,21 +2517,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2528,10 +2533,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120496936</v>
+        <v>120497044</v>
       </c>
       <c r="B17" t="n">
-        <v>5189</v>
+        <v>90580</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2540,43 +2545,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655210</v>
+        <v>655213</v>
       </c>
       <c r="R17" t="n">
-        <v>6681498</v>
+        <v>6681503</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2660,7 +2660,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120500284</v>
+        <v>120499637</v>
       </c>
       <c r="B18" t="n">
         <v>91200</v>
@@ -2700,10 +2700,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655136</v>
+        <v>654995</v>
       </c>
       <c r="R18" t="n">
-        <v>6681501</v>
+        <v>6681443</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2787,7 +2787,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120498166</v>
+        <v>120498244</v>
       </c>
       <c r="B19" t="n">
         <v>91200</v>
@@ -2827,10 +2827,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655161</v>
+        <v>655170</v>
       </c>
       <c r="R19" t="n">
-        <v>6681506</v>
+        <v>6681498</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2872,12 +2872,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Med gigantisk klibbticka.</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2919,10 +2914,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120499168</v>
+        <v>120498000</v>
       </c>
       <c r="B20" t="n">
-        <v>90781</v>
+        <v>91200</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2931,38 +2926,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1106</v>
+        <v>1339</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654913</v>
+        <v>655170</v>
       </c>
       <c r="R20" t="n">
-        <v>6681354</v>
+        <v>6681510</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2994,7 +2989,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -3004,7 +2999,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3046,7 +3041,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120498244</v>
+        <v>120500284</v>
       </c>
       <c r="B21" t="n">
         <v>91200</v>
@@ -3086,10 +3081,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>655170</v>
+        <v>655136</v>
       </c>
       <c r="R21" t="n">
-        <v>6681498</v>
+        <v>6681501</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3121,7 +3116,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3131,7 +3126,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3173,10 +3168,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120498000</v>
+        <v>120499168</v>
       </c>
       <c r="B22" t="n">
-        <v>91200</v>
+        <v>90781</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3185,38 +3180,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1339</v>
+        <v>1106</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655170</v>
+        <v>654913</v>
       </c>
       <c r="R22" t="n">
-        <v>6681510</v>
+        <v>6681354</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3248,7 +3243,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3258,7 +3253,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3300,7 +3295,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120499637</v>
+        <v>120498166</v>
       </c>
       <c r="B23" t="n">
         <v>91200</v>
@@ -3340,10 +3335,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654995</v>
+        <v>655161</v>
       </c>
       <c r="R23" t="n">
-        <v>6681443</v>
+        <v>6681506</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3375,7 +3370,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3385,7 +3380,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Med gigantisk klibbticka.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3564,10 +3564,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120535635</v>
+        <v>120534702</v>
       </c>
       <c r="B25" t="n">
-        <v>80499</v>
+        <v>90598</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3580,37 +3580,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1049</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654985</v>
+        <v>654972</v>
       </c>
       <c r="R25" t="n">
-        <v>6681219</v>
+        <v>6681278</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3642,7 +3639,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3652,12 +3649,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Riklig förekomst på gammal torr stubbe med gul, hård ved.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3666,9 +3658,23 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3685,10 +3691,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120534782</v>
+        <v>120533398</v>
       </c>
       <c r="B26" t="n">
-        <v>80499</v>
+        <v>57473</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3701,37 +3707,49 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654967</v>
+        <v>655229</v>
       </c>
       <c r="R26" t="n">
-        <v>6681292</v>
+        <v>6681479</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3760,7 +3778,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3770,7 +3788,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3793,14 +3811,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120497208</v>
+        <v>120499974</v>
       </c>
       <c r="B27" t="n">
-        <v>94550</v>
+        <v>91879</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3813,31 +3835,31 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>210</v>
+        <v>5964</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>kapslar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3846,10 +3868,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655213</v>
+        <v>655059</v>
       </c>
       <c r="R27" t="n">
-        <v>6681513</v>
+        <v>6681472</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3881,7 +3903,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3891,7 +3913,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bara gran och björk i närheten.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3902,21 +3929,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3933,14 +3945,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120497440</v>
+        <v>120533496</v>
       </c>
       <c r="B28" t="n">
-        <v>94550</v>
+        <v>100194</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3949,46 +3961,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>210</v>
+        <v>222498</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655206</v>
+        <v>655277</v>
       </c>
       <c r="R28" t="n">
-        <v>6681520</v>
+        <v>6681282</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4012,22 +4015,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bara enstaka plantor.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4038,21 +4046,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4069,65 +4062,62 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120533398</v>
+        <v>120497440</v>
       </c>
       <c r="B29" t="n">
-        <v>57473</v>
+        <v>94550</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>655229</v>
+        <v>655206</v>
       </c>
       <c r="R29" t="n">
-        <v>6681479</v>
+        <v>6681520</v>
       </c>
       <c r="S29" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4151,22 +4141,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4177,6 +4167,21 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4189,15 +4194,11 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120534340</v>
+        <v>120537301</v>
       </c>
       <c r="B30" t="n">
         <v>100194</v>
@@ -4237,10 +4238,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655029</v>
+        <v>655025</v>
       </c>
       <c r="R30" t="n">
-        <v>6681228</v>
+        <v>6681224</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4272,7 +4273,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4282,12 +4283,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:27</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Enstaka plantor.</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4314,10 +4310,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120537714</v>
+        <v>120536842</v>
       </c>
       <c r="B31" t="n">
-        <v>94454</v>
+        <v>5189</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4330,38 +4326,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>655100</v>
+        <v>654967</v>
       </c>
       <c r="R31" t="n">
-        <v>6681222</v>
+        <v>6681250</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4393,7 +4390,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4403,12 +4400,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På klen, riktigt murken granlåga i fuktig miljö.</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4417,7 +4409,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4451,10 +4442,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120538144</v>
+        <v>120535635</v>
       </c>
       <c r="B32" t="n">
-        <v>91512</v>
+        <v>80499</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4463,47 +4454,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4769</v>
+        <v>1049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655174</v>
+        <v>654985</v>
       </c>
       <c r="R32" t="n">
-        <v>6681223</v>
+        <v>6681219</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4535,7 +4520,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4545,12 +4530,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>I bättre begagnat skick. Bara gran runtom.</t>
+          <t>Riklig förekomst på gammal torr stubbe med gul, hård ved.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4559,6 +4544,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4577,10 +4563,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120535048</v>
+        <v>120534972</v>
       </c>
       <c r="B33" t="n">
-        <v>5189</v>
+        <v>100194</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4593,39 +4579,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654966</v>
+        <v>654933</v>
       </c>
       <c r="R33" t="n">
-        <v>6681257</v>
+        <v>6681283</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4657,7 +4638,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4667,7 +4648,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4678,21 +4659,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4709,14 +4675,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120499974</v>
+        <v>120533674</v>
       </c>
       <c r="B34" t="n">
-        <v>91879</v>
+        <v>103441</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4725,46 +4691,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5964</v>
+        <v>222412</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655059</v>
+        <v>655158</v>
       </c>
       <c r="R34" t="n">
-        <v>6681472</v>
+        <v>6681101</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4788,27 +4745,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Bara gran och björk i närheten.</t>
+          <t>Några småplantor.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4835,10 +4792,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120537910</v>
+        <v>120534782</v>
       </c>
       <c r="B35" t="n">
-        <v>5189</v>
+        <v>80499</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4847,43 +4804,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>105930</v>
+        <v>1049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>655176</v>
+        <v>654967</v>
       </c>
       <c r="R35" t="n">
-        <v>6681218</v>
+        <v>6681292</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4915,7 +4867,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4925,7 +4877,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4936,21 +4888,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4967,10 +4904,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120534972</v>
+        <v>120537714</v>
       </c>
       <c r="B36" t="n">
-        <v>100194</v>
+        <v>94454</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4983,34 +4920,38 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654933</v>
+        <v>655100</v>
       </c>
       <c r="R36" t="n">
-        <v>6681283</v>
+        <v>6681222</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5042,7 +4983,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5052,7 +4993,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På klen, riktigt murken granlåga i fuktig miljö.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5061,8 +5007,24 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -5079,10 +5041,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120537301</v>
+        <v>120538144</v>
       </c>
       <c r="B37" t="n">
-        <v>100194</v>
+        <v>91512</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -5095,34 +5057,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222498</v>
+        <v>4769</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655025</v>
+        <v>655174</v>
       </c>
       <c r="R37" t="n">
-        <v>6681224</v>
+        <v>6681223</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -5154,7 +5125,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -5164,7 +5135,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>I bättre begagnat skick. Bara gran runtom.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5191,10 +5167,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120525413</v>
+        <v>120497208</v>
       </c>
       <c r="B38" t="n">
-        <v>94454</v>
+        <v>94550</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5207,41 +5183,46 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>655206</v>
+        <v>655213</v>
       </c>
       <c r="R38" t="n">
-        <v>6681520</v>
+        <v>6681513</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5270,7 +5251,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5280,12 +5261,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På samma låga som grön sköldmossa.</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5294,7 +5270,6 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -5328,10 +5303,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120533674</v>
+        <v>120534505</v>
       </c>
       <c r="B39" t="n">
-        <v>103441</v>
+        <v>5189</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5344,34 +5319,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>655158</v>
+        <v>655054</v>
       </c>
       <c r="R39" t="n">
-        <v>6681101</v>
+        <v>6681371</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5403,7 +5383,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5413,12 +5393,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Några småplantor.</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5445,14 +5420,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120534339</v>
+        <v>120525413</v>
       </c>
       <c r="B40" t="n">
-        <v>5189</v>
+        <v>94454</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5461,39 +5436,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655046</v>
+        <v>655206</v>
       </c>
       <c r="R40" t="n">
-        <v>6681223</v>
+        <v>6681520</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5520,22 +5494,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På samma låga som grön sköldmossa.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5544,6 +5523,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5689,10 +5669,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120534702</v>
+        <v>120533945</v>
       </c>
       <c r="B42" t="n">
-        <v>90598</v>
+        <v>5189</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5701,38 +5681,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>105930</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654972</v>
+        <v>655142</v>
       </c>
       <c r="R42" t="n">
-        <v>6681278</v>
+        <v>6681116</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5764,7 +5749,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5774,7 +5759,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5785,21 +5770,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5816,10 +5786,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120533496</v>
+        <v>120534339</v>
       </c>
       <c r="B43" t="n">
-        <v>100194</v>
+        <v>5189</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5832,34 +5802,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>222498</v>
+        <v>105930</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655277</v>
+        <v>655046</v>
       </c>
       <c r="R43" t="n">
-        <v>6681282</v>
+        <v>6681223</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5891,7 +5866,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5901,12 +5876,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Bara enstaka plantor.</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5917,6 +5887,21 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5933,7 +5918,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120533945</v>
+        <v>120535048</v>
       </c>
       <c r="B44" t="n">
         <v>5189</v>
@@ -5974,14 +5959,14 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>655142</v>
+        <v>654966</v>
       </c>
       <c r="R44" t="n">
-        <v>6681116</v>
+        <v>6681257</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -6013,7 +5998,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -6023,7 +6008,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6034,6 +6019,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6050,7 +6050,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120534505</v>
+        <v>120537910</v>
       </c>
       <c r="B45" t="n">
         <v>5189</v>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655054</v>
+        <v>655176</v>
       </c>
       <c r="R45" t="n">
-        <v>6681371</v>
+        <v>6681218</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6151,6 +6151,21 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6167,10 +6182,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120536842</v>
+        <v>120534340</v>
       </c>
       <c r="B46" t="n">
-        <v>5189</v>
+        <v>100194</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -6183,39 +6198,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>105930</v>
+        <v>222498</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654967</v>
+        <v>655029</v>
       </c>
       <c r="R46" t="n">
-        <v>6681250</v>
+        <v>6681228</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -6247,7 +6257,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6257,7 +6267,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Enstaka plantor.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6268,21 +6283,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6296,6 +6296,397 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>120534851</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>654967</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6681293</v>
+      </c>
+      <c r="S47" t="n">
+        <v>5</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>120537189</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>654971</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6681242</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:04</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>120534558</v>
+      </c>
+      <c r="B49" t="n">
+        <v>91200</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>655023</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6681343</v>
+      </c>
+      <c r="S49" t="n">
+        <v>5</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY49"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120498166</v>
+        <v>120525350</v>
       </c>
       <c r="B23" t="n">
-        <v>91200</v>
+        <v>94454</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3311,37 +3311,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655161</v>
+        <v>655231</v>
       </c>
       <c r="R23" t="n">
-        <v>6681506</v>
+        <v>6681523</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3370,7 +3374,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3380,12 +3384,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Med gigantisk klibbticka.</t>
+          <t>På samma låga som grön sköldmossa.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3394,6 +3398,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3427,10 +3432,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120525350</v>
+        <v>120498166</v>
       </c>
       <c r="B24" t="n">
-        <v>94454</v>
+        <v>91200</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3443,41 +3448,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655231</v>
+        <v>655161</v>
       </c>
       <c r="R24" t="n">
-        <v>6681523</v>
+        <v>6681506</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3506,7 +3507,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3516,12 +3517,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På samma låga som grön sköldmossa.</t>
+          <t>Med gigantisk klibbticka.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3530,7 +3531,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -4675,10 +4675,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120533674</v>
+        <v>120534782</v>
       </c>
       <c r="B34" t="n">
-        <v>103441</v>
+        <v>80499</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4687,38 +4687,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222412</v>
+        <v>1049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655158</v>
+        <v>654967</v>
       </c>
       <c r="R34" t="n">
-        <v>6681101</v>
+        <v>6681292</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4760,12 +4760,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Några småplantor.</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4792,10 +4787,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120534782</v>
+        <v>120537714</v>
       </c>
       <c r="B35" t="n">
-        <v>80499</v>
+        <v>94454</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4804,38 +4799,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1049</v>
+        <v>2818</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654967</v>
+        <v>655100</v>
       </c>
       <c r="R35" t="n">
-        <v>6681292</v>
+        <v>6681222</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4867,7 +4866,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4877,7 +4876,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På klen, riktigt murken granlåga i fuktig miljö.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4886,8 +4890,24 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4904,10 +4924,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120537714</v>
+        <v>120533674</v>
       </c>
       <c r="B36" t="n">
-        <v>94454</v>
+        <v>103441</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4920,38 +4940,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2818</v>
+        <v>222412</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655100</v>
+        <v>655158</v>
       </c>
       <c r="R36" t="n">
-        <v>6681222</v>
+        <v>6681101</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4983,7 +4999,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4993,12 +5009,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På klen, riktigt murken granlåga i fuktig miljö.</t>
+          <t>Några småplantor.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5007,24 +5023,8 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -6688,6 +6688,138 @@
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>120537533</v>
+      </c>
+      <c r="B50" t="n">
+        <v>4766</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>655048</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6681299</v>
+      </c>
+      <c r="S50" t="n">
+        <v>5</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -1767,11 +1767,11 @@
         <v>120498507</v>
       </c>
       <c r="B11" t="n">
-        <v>57501</v>
+        <v>57631</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2015,11 +2015,11 @@
         <v>120497099</v>
       </c>
       <c r="B13" t="n">
-        <v>57501</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5945,11 +5945,11 @@
         <v>120533398</v>
       </c>
       <c r="B44" t="n">
-        <v>57501</v>
+        <v>57631</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -7596,11 +7596,11 @@
         <v>120680550</v>
       </c>
       <c r="B57" t="n">
-        <v>57501</v>
+        <v>57631</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -1767,7 +1767,7 @@
         <v>120498507</v>
       </c>
       <c r="B11" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>120497099</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>120533398</v>
       </c>
       <c r="B44" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>120680550</v>
       </c>
       <c r="B57" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>

--- a/artfynd/A 45170-2024 artfynd.xlsx
+++ b/artfynd/A 45170-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY63"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120229445</v>
+        <v>120496798</v>
       </c>
       <c r="B2" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>105930</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>655214</v>
+        <v>655231</v>
       </c>
       <c r="R2" t="n">
-        <v>6681515</v>
+        <v>6681523</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,6 +775,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,15 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120229626</v>
+        <v>120497208</v>
       </c>
       <c r="B3" t="n">
-        <v>103441</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,41 +817,46 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>210</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>655258</v>
+        <v>655213</v>
       </c>
       <c r="R3" t="n">
-        <v>6681471</v>
+        <v>6681513</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -870,22 +880,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,6 +906,21 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -912,15 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120229494</v>
+        <v>120497440</v>
       </c>
       <c r="B4" t="n">
-        <v>91200</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,40 +948,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1339</v>
+        <v>210</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>655013</v>
+        <v>655206</v>
       </c>
       <c r="R4" t="n">
-        <v>6681312</v>
+        <v>6681520</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,22 +1011,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,6 +1037,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1027,15 +1068,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120229510</v>
+        <v>120678530</v>
       </c>
       <c r="B5" t="n">
-        <v>91272</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,40 +1079,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>655235</v>
+        <v>655242</v>
       </c>
       <c r="R5" t="n">
-        <v>6681455</v>
+        <v>6681514</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1100,22 +1133,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,6 +1159,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1142,56 +1190,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120229499</v>
+        <v>120534782</v>
       </c>
       <c r="B6" t="n">
-        <v>91200</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1339</v>
+        <v>1049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>655191</v>
+        <v>654967</v>
       </c>
       <c r="R6" t="n">
-        <v>6681506</v>
+        <v>6681292</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,22 +1255,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-05</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,15 +1297,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120497044</v>
+        <v>120535635</v>
       </c>
       <c r="B7" t="n">
-        <v>90679</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,37 +1308,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>655213</v>
+        <v>654985</v>
       </c>
       <c r="R7" t="n">
-        <v>6681503</v>
+        <v>6681219</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1327,22 +1365,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig förekomst på gammal torr stubbe med gul, hård ved.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1351,23 +1394,9 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1384,15 +1413,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120497668</v>
+        <v>120499168</v>
       </c>
       <c r="B8" t="n">
-        <v>57354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1400,46 +1424,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100048</v>
+        <v>1106</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>655206</v>
+        <v>654913</v>
       </c>
       <c r="R8" t="n">
-        <v>6681496</v>
+        <v>6681354</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1468,7 +1483,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,7 +1493,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,6 +1504,21 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1505,55 +1535,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120498279</v>
+        <v>120497044</v>
       </c>
       <c r="B9" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>655176</v>
+        <v>655213</v>
       </c>
       <c r="R9" t="n">
-        <v>6681491</v>
+        <v>6681503</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1585,7 +1605,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1595,7 +1615,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:07</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,15 +1657,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120499877</v>
+        <v>120229494</v>
       </c>
       <c r="B10" t="n">
-        <v>91362</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1653,37 +1668,40 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>655044</v>
+        <v>655013</v>
       </c>
       <c r="R10" t="n">
-        <v>6681469</v>
+        <v>6681312</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1707,22 +1725,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,21 +1751,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1764,62 +1767,51 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120498507</v>
+        <v>120229498</v>
       </c>
       <c r="B11" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>655132</v>
+        <v>655196</v>
       </c>
       <c r="R11" t="n">
-        <v>6681443</v>
+        <v>6681514</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1843,22 +1835,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1885,15 +1877,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120500418</v>
+        <v>120229499</v>
       </c>
       <c r="B12" t="n">
-        <v>91294</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1919,19 +1906,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>655161</v>
+        <v>655191</v>
       </c>
       <c r="R12" t="n">
-        <v>6681641</v>
+        <v>6681506</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1955,22 +1945,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1981,21 +1971,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2012,62 +1987,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120497099</v>
+        <v>120498000</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1339</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>655229</v>
+        <v>655170</v>
       </c>
       <c r="R13" t="n">
-        <v>6681516</v>
+        <v>6681510</v>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2106,7 +2067,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2117,6 +2078,21 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2133,15 +2109,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120496798</v>
+        <v>120498166</v>
       </c>
       <c r="B14" t="n">
-        <v>94669</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2149,43 +2120,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>210</v>
+        <v>1339</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>655231</v>
+        <v>655161</v>
       </c>
       <c r="R14" t="n">
-        <v>6681523</v>
+        <v>6681506</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2217,7 +2179,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2227,7 +2189,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Med gigantisk klibbticka.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2269,15 +2236,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120495656</v>
+        <v>120498244</v>
       </c>
       <c r="B15" t="n">
-        <v>90663</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2285,34 +2247,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4660</v>
+        <v>1339</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rävticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Inocutis rheades</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>655401</v>
+        <v>655170</v>
       </c>
       <c r="R15" t="n">
-        <v>6681567</v>
+        <v>6681498</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2344,7 +2306,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2354,7 +2316,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2368,17 +2330,17 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2396,15 +2358,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120499836</v>
+        <v>120499637</v>
       </c>
       <c r="B16" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2412,39 +2369,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>655037</v>
+        <v>654995</v>
       </c>
       <c r="R16" t="n">
-        <v>6681471</v>
+        <v>6681443</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2476,7 +2428,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2486,7 +2438,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2528,15 +2480,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120496936</v>
+        <v>120500284</v>
       </c>
       <c r="B17" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2544,39 +2491,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>1339</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>655210</v>
+        <v>655136</v>
       </c>
       <c r="R17" t="n">
-        <v>6681498</v>
+        <v>6681501</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2608,7 +2550,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2618,7 +2560,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2660,15 +2602,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120498000</v>
+        <v>120500418</v>
       </c>
       <c r="B18" t="n">
-        <v>91294</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2700,10 +2637,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>655170</v>
+        <v>655161</v>
       </c>
       <c r="R18" t="n">
-        <v>6681510</v>
+        <v>6681641</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2735,7 +2672,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2745,7 +2682,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2787,15 +2724,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120525350</v>
+        <v>120534558</v>
       </c>
       <c r="B19" t="n">
-        <v>94577</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2803,38 +2735,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2818</v>
+        <v>1339</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>655231</v>
+        <v>655023</v>
       </c>
       <c r="R19" t="n">
-        <v>6681523</v>
+        <v>6681343</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2861,27 +2789,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På samma låga som grön sköldmossa.</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2890,7 +2813,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2924,15 +2846,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120499637</v>
+        <v>120681093</v>
       </c>
       <c r="B20" t="n">
-        <v>91294</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92564</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2964,13 +2881,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654995</v>
+        <v>655196</v>
       </c>
       <c r="R20" t="n">
-        <v>6681443</v>
+        <v>6681465</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2994,22 +2911,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3051,53 +2968,52 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120499168</v>
+        <v>120525350</v>
       </c>
       <c r="B21" t="n">
-        <v>90883</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1106</v>
+        <v>2818</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654913</v>
+        <v>655231</v>
       </c>
       <c r="R21" t="n">
-        <v>6681354</v>
+        <v>6681523</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3126,7 +3042,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3136,7 +3052,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På samma låga som grön sköldmossa.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3145,6 +3066,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3178,15 +3100,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120498244</v>
+        <v>120525413</v>
       </c>
       <c r="B22" t="n">
-        <v>91294</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3194,37 +3111,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>655170</v>
+        <v>655206</v>
       </c>
       <c r="R22" t="n">
-        <v>6681498</v>
+        <v>6681520</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3253,7 +3174,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3263,7 +3184,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På samma låga som grön sköldmossa.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3272,6 +3198,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3305,15 +3232,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120498166</v>
+        <v>120537714</v>
       </c>
       <c r="B23" t="n">
-        <v>91294</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3321,37 +3243,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>655161</v>
+        <v>655100</v>
       </c>
       <c r="R23" t="n">
-        <v>6681506</v>
+        <v>6681222</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3375,27 +3301,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Med gigantisk klibbticka.</t>
+          <t>På klen, riktigt murken granlåga i fuktig miljö.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3404,6 +3330,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3437,15 +3364,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120500284</v>
+        <v>120678355</v>
       </c>
       <c r="B24" t="n">
-        <v>91294</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3453,21 +3375,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1339</v>
+        <v>2818</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3477,13 +3399,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>655136</v>
+        <v>655223</v>
       </c>
       <c r="R24" t="n">
-        <v>6681501</v>
+        <v>6681513</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3507,22 +3429,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3533,21 +3455,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3564,15 +3471,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120537714</v>
+        <v>120678495</v>
       </c>
       <c r="B25" t="n">
-        <v>94577</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3598,20 +3500,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>655100</v>
+        <v>655241</v>
       </c>
       <c r="R25" t="n">
-        <v>6681222</v>
+        <v>6681516</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3638,27 +3536,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:40</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>På klen, riktigt murken granlåga i fuktig miljö.</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3667,7 +3560,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3701,15 +3593,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>120533660</v>
+        <v>120681519</v>
       </c>
       <c r="B26" t="n">
-        <v>100320</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3717,34 +3604,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>655173</v>
+        <v>655202</v>
       </c>
       <c r="R26" t="n">
-        <v>6681110</v>
+        <v>6681502</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3771,22 +3658,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3797,6 +3684,21 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3813,15 +3715,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120533496</v>
+        <v>120683580</v>
       </c>
       <c r="B27" t="n">
-        <v>100320</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3829,34 +3726,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>655277</v>
+        <v>655185</v>
       </c>
       <c r="R27" t="n">
-        <v>6681282</v>
+        <v>6681633</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3883,27 +3780,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:54</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Bara enstaka plantor.</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3914,6 +3806,21 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3930,15 +3837,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120534339</v>
+        <v>120685794</v>
       </c>
       <c r="B28" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3946,39 +3848,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>2818</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>655046</v>
+        <v>655233</v>
       </c>
       <c r="R28" t="n">
-        <v>6681223</v>
+        <v>6681530</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4005,22 +3902,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4031,21 +3928,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -4062,53 +3944,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120535635</v>
+        <v>120686067</v>
       </c>
       <c r="B29" t="n">
-        <v>80551</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1049</v>
+        <v>2818</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654985</v>
+        <v>655271</v>
       </c>
       <c r="R29" t="n">
-        <v>6681219</v>
+        <v>6681527</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -4135,27 +4009,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:09</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Riklig förekomst på gammal torr stubbe med gul, hård ved.</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4164,9 +4033,23 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4183,15 +4066,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120537301</v>
+        <v>120686152</v>
       </c>
       <c r="B30" t="n">
-        <v>100320</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4199,34 +4077,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222498</v>
+        <v>2818</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>655025</v>
+        <v>655287</v>
       </c>
       <c r="R30" t="n">
-        <v>6681224</v>
+        <v>6681536</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4253,22 +4131,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4295,15 +4173,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120536842</v>
+        <v>120229506</v>
       </c>
       <c r="B31" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4311,42 +4184,40 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654967</v>
+        <v>655185</v>
       </c>
       <c r="R31" t="n">
-        <v>6681250</v>
+        <v>6681566</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4370,22 +4241,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4396,21 +4267,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4427,15 +4283,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>120525413</v>
+        <v>120229510</v>
       </c>
       <c r="B32" t="n">
-        <v>94577</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4443,27 +4294,26 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2818</v>
+        <v>3298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -4471,13 +4321,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>655206</v>
+        <v>655235</v>
       </c>
       <c r="R32" t="n">
-        <v>6681520</v>
+        <v>6681455</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4501,27 +4351,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:10</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På samma låga som grön sköldmossa.</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,24 +4375,8 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4564,15 +4393,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120535048</v>
+        <v>120497767</v>
       </c>
       <c r="B33" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4580,42 +4404,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654966</v>
+        <v>655185</v>
       </c>
       <c r="R33" t="n">
-        <v>6681257</v>
+        <v>6681550</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4639,22 +4458,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4696,15 +4515,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>120534505</v>
+        <v>120499877</v>
       </c>
       <c r="B34" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4712,42 +4526,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>105930</v>
+        <v>3298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>655054</v>
+        <v>655044</v>
       </c>
       <c r="R34" t="n">
-        <v>6681371</v>
+        <v>6681469</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4771,22 +4580,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4797,6 +4606,21 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4813,53 +4637,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120534702</v>
+        <v>120495656</v>
       </c>
       <c r="B35" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>4660</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rävticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Inocutis rheades</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654972</v>
+        <v>655401</v>
       </c>
       <c r="R35" t="n">
-        <v>6681278</v>
+        <v>6681567</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4883,22 +4702,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4912,17 +4731,17 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4940,15 +4759,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120533674</v>
+        <v>120538144</v>
       </c>
       <c r="B36" t="n">
-        <v>103568</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92869</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4956,34 +4770,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>222412</v>
+        <v>4769</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>655158</v>
+        <v>655174</v>
       </c>
       <c r="R36" t="n">
-        <v>6681101</v>
+        <v>6681223</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -5015,7 +4838,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -5025,19 +4848,19 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Några småplantor.</t>
+          <t>I bättre begagnat skick. Bara gran runtom.</t>
         </is>
       </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG36" t="b">
         <v>0</v>
@@ -5057,58 +4880,57 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120533945</v>
+        <v>120499974</v>
       </c>
       <c r="B37" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>105930</v>
+        <v>5964</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>655142</v>
+        <v>655059</v>
       </c>
       <c r="R37" t="n">
-        <v>6681116</v>
+        <v>6681472</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5132,22 +4954,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bara gran och björk i närheten.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5174,53 +5001,48 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120534972</v>
+        <v>120497612</v>
       </c>
       <c r="B38" t="n">
-        <v>100320</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91738</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222498</v>
+        <v>6020</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Oljetagging</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sistotrema raduloides</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Donk</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654933</v>
+        <v>655191</v>
       </c>
       <c r="R38" t="n">
-        <v>6681283</v>
+        <v>6681533</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5244,22 +5066,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Karakteristisk doft - stark, syrlig, ”kemiskt fruktig”.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5270,6 +5097,21 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5286,47 +5128,42 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120497440</v>
+        <v>120497668</v>
       </c>
       <c r="B39" t="n">
-        <v>94673</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>210</v>
+        <v>100048</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5338,10 +5175,10 @@
         <v>655206</v>
       </c>
       <c r="R39" t="n">
-        <v>6681520</v>
+        <v>6681496</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5370,7 +5207,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5380,7 +5217,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5391,21 +5228,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5422,47 +5244,47 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120497208</v>
+        <v>120681321</v>
       </c>
       <c r="B40" t="n">
-        <v>94673</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57966</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>210</v>
+        <v>100048</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>kapslar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5471,13 +5293,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>655213</v>
+        <v>655161</v>
       </c>
       <c r="R40" t="n">
-        <v>6681513</v>
+        <v>6681466</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5501,22 +5323,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Födosöker frenetiskt ute på grenar högt upp.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5558,15 +5385,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120537910</v>
+        <v>120534851</v>
       </c>
       <c r="B41" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5574,16 +5396,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>105930</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5594,19 +5416,19 @@
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>655176</v>
+        <v>654967</v>
       </c>
       <c r="R41" t="n">
-        <v>6681218</v>
+        <v>6681293</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5638,7 +5460,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5648,7 +5470,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5690,15 +5512,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120499974</v>
+        <v>120537189</v>
       </c>
       <c r="B42" t="n">
-        <v>91988</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5706,46 +5523,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5964</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>655059</v>
+        <v>654971</v>
       </c>
       <c r="R42" t="n">
-        <v>6681472</v>
+        <v>6681242</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5769,27 +5582,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Bara gran och björk i närheten.</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5800,6 +5608,21 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5816,15 +5639,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120538144</v>
+        <v>120537533</v>
       </c>
       <c r="B43" t="n">
-        <v>91612</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5832,43 +5650,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4769</v>
+        <v>100299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Rundbodiket, Rundbodiket, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>655174</v>
+        <v>655048</v>
       </c>
       <c r="R43" t="n">
-        <v>6681223</v>
+        <v>6681299</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5900,7 +5718,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5910,22 +5728,33 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>I bättre begagnat skick. Bara gran runtom.</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
       <c r="AE43" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5942,65 +5771,53 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120533398</v>
+        <v>120498279</v>
       </c>
       <c r="B44" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>655229</v>
+        <v>655176</v>
       </c>
       <c r="R44" t="n">
-        <v>6681479</v>
+        <v>6681491</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -6024,22 +5841,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>15:07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6050,6 +5867,21 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -6062,23 +5894,14 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY44" t="inlineStr">
-        <is>
-          <t>EKOLISTAN</t>
-        </is>
-      </c>
+      <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120534340</v>
+        <v>120680299</v>
       </c>
       <c r="B45" t="n">
-        <v>100320</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -6086,34 +5909,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>222498</v>
+        <v>100526</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>655029</v>
+        <v>655222</v>
       </c>
       <c r="R45" t="n">
-        <v>6681228</v>
+        <v>6681509</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -6140,37 +5963,52 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:27</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Enstaka plantor.</t>
+          <t>Kläckhål 6 mm breda men gångarna inte helt typiska.</t>
         </is>
       </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
       <c r="AE45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -6187,15 +6025,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120534782</v>
+        <v>120497099</v>
       </c>
       <c r="B46" t="n">
-        <v>80551</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6203,37 +6036,46 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1049</v>
+        <v>103021</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654967</v>
+        <v>655229</v>
       </c>
       <c r="R46" t="n">
-        <v>6681292</v>
+        <v>6681516</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6257,22 +6099,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6299,15 +6141,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120534851</v>
+        <v>120498507</v>
       </c>
       <c r="B47" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6315,42 +6152,46 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654967</v>
+        <v>655132</v>
       </c>
       <c r="R47" t="n">
-        <v>6681293</v>
+        <v>6681443</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6374,22 +6215,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6400,21 +6241,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -6431,53 +6257,60 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120534558</v>
+        <v>120533398</v>
       </c>
       <c r="B48" t="n">
-        <v>91294</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1339</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>655023</v>
+        <v>655229</v>
       </c>
       <c r="R48" t="n">
-        <v>6681343</v>
+        <v>6681479</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6506,7 +6339,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6516,7 +6349,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6527,21 +6360,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6554,19 +6372,18 @@
           <t>Annika Rastén</t>
         </is>
       </c>
-      <c r="AY48" t="inlineStr"/>
+      <c r="AY48" t="inlineStr">
+        <is>
+          <t>EKOLISTAN</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120537189</v>
+        <v>120680550</v>
       </c>
       <c r="B49" t="n">
-        <v>57364</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6574,42 +6391,46 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Hällsmyren, Hällsmyren, Upl</t>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654971</v>
+        <v>655200</v>
       </c>
       <c r="R49" t="n">
-        <v>6681242</v>
+        <v>6681455</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6633,22 +6454,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-26</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:04</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6659,21 +6480,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6690,15 +6496,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120537533</v>
+        <v>120229442</v>
       </c>
       <c r="B50" t="n">
-        <v>4766</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6706,21 +6507,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100299</v>
+        <v>105930</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6735,17 +6536,17 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>655048</v>
+        <v>655240</v>
       </c>
       <c r="R50" t="n">
-        <v>6681299</v>
+        <v>6681556</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6769,22 +6570,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-10-21</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6793,24 +6594,8 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6827,15 +6612,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120681093</v>
+        <v>120229445</v>
       </c>
       <c r="B51" t="n">
-        <v>91294</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6843,37 +6623,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1339</v>
+        <v>105930</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>655196</v>
+        <v>655214</v>
       </c>
       <c r="R51" t="n">
-        <v>6681465</v>
+        <v>6681515</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6897,22 +6686,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-05</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6923,21 +6712,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6954,32 +6728,27 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120681321</v>
+        <v>120496936</v>
       </c>
       <c r="B52" t="n">
-        <v>57354</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100048</v>
+        <v>105930</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6987,19 +6756,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -7008,13 +6768,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>655161</v>
+        <v>655210</v>
       </c>
       <c r="R52" t="n">
-        <v>6681466</v>
+        <v>6681498</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -7038,27 +6798,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Födosöker frenetiskt ute på grenar högt upp.</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -7100,15 +6855,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120678530</v>
+        <v>120497526</v>
       </c>
       <c r="B53" t="n">
-        <v>94675</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7116,37 +6866,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>210</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>655242</v>
+        <v>655196</v>
       </c>
       <c r="R53" t="n">
-        <v>6681514</v>
+        <v>6681537</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -7170,22 +6925,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7227,15 +6982,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120680299</v>
+        <v>120497880</v>
       </c>
       <c r="B54" t="n">
-        <v>5169</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7243,37 +6993,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>105930</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>655222</v>
+        <v>655188</v>
       </c>
       <c r="R54" t="n">
-        <v>6681509</v>
+        <v>6681556</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -7297,34 +7052,29 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:12</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Kläckhål 6 mm breda men gångarna inte helt typiska.</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG54" t="b">
         <v>0</v>
@@ -7359,15 +7109,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120685869</v>
+        <v>120497929</v>
       </c>
       <c r="B55" t="n">
-        <v>103570</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7375,37 +7120,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>222412</v>
+        <v>105930</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>655241</v>
+        <v>655177</v>
       </c>
       <c r="R55" t="n">
-        <v>6681533</v>
+        <v>6681550</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7429,22 +7179,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7455,6 +7205,21 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7471,48 +7236,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120680773</v>
+        <v>120499836</v>
       </c>
       <c r="B56" t="n">
-        <v>91072</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6040186</v>
+        <v>105930</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>655210</v>
+        <v>655037</v>
       </c>
       <c r="R56" t="n">
-        <v>6681444</v>
+        <v>6681471</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7536,22 +7306,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7593,62 +7363,53 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120680550</v>
+        <v>120533945</v>
       </c>
       <c r="B57" t="n">
-        <v>57634</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>103021</v>
+        <v>105930</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>655200</v>
+        <v>655142</v>
       </c>
       <c r="R57" t="n">
-        <v>6681455</v>
+        <v>6681116</v>
       </c>
       <c r="S57" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7672,22 +7433,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7714,15 +7475,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120680608</v>
+        <v>120534339</v>
       </c>
       <c r="B58" t="n">
-        <v>5189</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7750,19 +7506,19 @@
       <c r="I58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>655222</v>
+        <v>655046</v>
       </c>
       <c r="R58" t="n">
-        <v>6681466</v>
+        <v>6681223</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -7789,22 +7545,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7846,15 +7602,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120681519</v>
+        <v>120534505</v>
       </c>
       <c r="B59" t="n">
-        <v>94579</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7862,34 +7613,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>655202</v>
+        <v>655054</v>
       </c>
       <c r="R59" t="n">
-        <v>6681502</v>
+        <v>6681371</v>
       </c>
       <c r="S59" t="n">
         <v>5</v>
@@ -7916,22 +7672,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7942,21 +7698,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7973,15 +7714,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120686152</v>
+        <v>120535048</v>
       </c>
       <c r="B60" t="n">
-        <v>94579</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7989,34 +7725,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>655287</v>
+        <v>654966</v>
       </c>
       <c r="R60" t="n">
-        <v>6681536</v>
+        <v>6681257</v>
       </c>
       <c r="S60" t="n">
         <v>5</v>
@@ -8043,22 +7784,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -8069,6 +7810,21 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -8085,15 +7841,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120678355</v>
+        <v>120536842</v>
       </c>
       <c r="B61" t="n">
-        <v>94579</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -8101,34 +7852,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>655223</v>
+        <v>654967</v>
       </c>
       <c r="R61" t="n">
-        <v>6681513</v>
+        <v>6681250</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -8155,22 +7911,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8181,6 +7937,21 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -8197,15 +7968,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120686067</v>
+        <v>120537910</v>
       </c>
       <c r="B62" t="n">
-        <v>94579</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8213,34 +7979,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>655271</v>
+        <v>655176</v>
       </c>
       <c r="R62" t="n">
-        <v>6681527</v>
+        <v>6681218</v>
       </c>
       <c r="S62" t="n">
         <v>5</v>
@@ -8267,22 +8038,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-10-26</t>
+          <t>2024-10-21</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -8324,15 +8095,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120678495</v>
+        <v>120680608</v>
       </c>
       <c r="B63" t="n">
-        <v>94579</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8340,34 +8106,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2818</v>
+        <v>105930</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>655241</v>
+        <v>655222</v>
       </c>
       <c r="R63" t="n">
-        <v>6681516</v>
+        <v>6681466</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -8399,7 +8170,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -8409,7 +8180,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>12:04</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8448,6 +8219,1110 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120684040</v>
+      </c>
+      <c r="B64" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>655192</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6681629</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:37</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120229626</v>
+      </c>
+      <c r="B65" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>655258</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6681471</v>
+      </c>
+      <c r="S65" t="n">
+        <v>4</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120533674</v>
+      </c>
+      <c r="B66" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>655158</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6681101</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Några småplantor.</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120685869</v>
+      </c>
+      <c r="B67" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>655241</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6681533</v>
+      </c>
+      <c r="S67" t="n">
+        <v>5</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120533496</v>
+      </c>
+      <c r="B68" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>655277</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6681282</v>
+      </c>
+      <c r="S68" t="n">
+        <v>5</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Bara enstaka plantor.</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120533660</v>
+      </c>
+      <c r="B69" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Rundbodiket, Rundbodiket, Upl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>655173</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6681110</v>
+      </c>
+      <c r="S69" t="n">
+        <v>5</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120534340</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>655029</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6681228</v>
+      </c>
+      <c r="S70" t="n">
+        <v>5</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Enstaka plantor.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120534972</v>
+      </c>
+      <c r="B71" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>654933</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6681283</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120537301</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hällsmyren, Hällsmyren, Upl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>655025</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6681224</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-21</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120680773</v>
+      </c>
+      <c r="B73" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Konstkarlsrönningen, Konstkarlsrönningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>655210</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6681444</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Film</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-26</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
